--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N223_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0001T0006Z000C1N223_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.19737184041639</v>
+        <v>2.794572924067664</v>
       </c>
       <c r="D2" t="n">
-        <v>43.748102491168</v>
+        <v>7.1090666548148</v>
       </c>
       <c r="E2" t="n">
-        <v>17.65381364703731</v>
+        <v>2.868744717643563</v>
       </c>
       <c r="F2" t="n">
-        <v>13.68618417259376</v>
+        <v>2.224004928046485</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>20.40833163195855</v>
+        <v>3.316353890193264</v>
       </c>
       <c r="D3" t="n">
-        <v>39.30183816603759</v>
+        <v>6.386548701981109</v>
       </c>
       <c r="E3" t="n">
-        <v>17.65381364703731</v>
+        <v>2.868744717643563</v>
       </c>
       <c r="F3" t="n">
-        <v>13.68618417259376</v>
+        <v>2.224004928046485</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.44066741267459</v>
+        <v>2.346608454559621</v>
       </c>
       <c r="D4" t="n">
-        <v>15.62912306007431</v>
+        <v>2.539732497262075</v>
       </c>
       <c r="E4" t="n">
-        <v>17.65381364703731</v>
+        <v>2.868744717643563</v>
       </c>
       <c r="F4" t="n">
-        <v>13.68618417259376</v>
+        <v>2.224004928046485</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>21.47826267671291</v>
+        <v>3.490217684965847</v>
       </c>
       <c r="D5" t="n">
-        <v>19.75503270358432</v>
+        <v>3.210192814332451</v>
       </c>
       <c r="E5" t="n">
-        <v>17.65381364703731</v>
+        <v>2.868744717643563</v>
       </c>
       <c r="F5" t="n">
-        <v>13.68618417259376</v>
+        <v>2.224004928046485</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.04248011316944</v>
+        <v>4.556903018390034</v>
       </c>
       <c r="D6" t="n">
-        <v>27.64718430881099</v>
+        <v>4.492667450181786</v>
       </c>
       <c r="E6" t="n">
-        <v>17.65381364703731</v>
+        <v>2.868744717643563</v>
       </c>
       <c r="F6" t="n">
-        <v>13.68618417259376</v>
+        <v>2.224004928046485</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6.876124094508562</v>
+        <v>1.117370165357641</v>
       </c>
       <c r="D7" t="n">
-        <v>5.829913444960279</v>
+        <v>0.9473609348060453</v>
       </c>
       <c r="E7" t="n">
-        <v>17.65381364703731</v>
+        <v>2.868744717643563</v>
       </c>
       <c r="F7" t="n">
-        <v>13.68618417259376</v>
+        <v>2.224004928046485</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>65.47430315750664</v>
+        <v>10.63957426309483</v>
       </c>
       <c r="D8" t="n">
-        <v>42.93261040079927</v>
+        <v>6.976549190129882</v>
       </c>
       <c r="E8" t="n">
-        <v>17.65381364703731</v>
+        <v>2.868744717643563</v>
       </c>
       <c r="F8" t="n">
-        <v>13.68618417259376</v>
+        <v>2.224004928046485</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
